--- a/data/trans_bre/P1419-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1419-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>125,1%</t>
+          <t>110,43%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 9,26</t>
+          <t>1,87; 9,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,28</t>
+          <t>1,36; 5,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,43</t>
+          <t>-1,1; 4,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,42</t>
+          <t>1,36; 6,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,78; 522,81</t>
+          <t>38,71; 526,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 377,06</t>
+          <t>-47,56; 311,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,01; 306,4</t>
+          <t>26,5; 248,45</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,82</t>
+          <t>5,17</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>151,32%</t>
+          <t>162,76%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,17</t>
+          <t>1,67; 7,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,61</t>
+          <t>1,85; 7,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,93</t>
+          <t>-0,09; 4,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,12</t>
+          <t>2,78; 7,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 589,22</t>
+          <t>37,84; 547,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,13; 2008,01</t>
+          <t>75,68; 2137,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 1447,28</t>
+          <t>-52,46; 1284,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,95; 347,64</t>
+          <t>60,55; 360,22</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,92</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>390,73%</t>
+          <t>221,27%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,51; 14,6</t>
+          <t>3,39; 14,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,84</t>
+          <t>3,4; 10,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 14,74</t>
+          <t>3,95; 14,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,97; 21,93</t>
+          <t>8,17; 18,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,74; 495,63</t>
+          <t>57,34; 498,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>149,03; 1461,65</t>
+          <t>125,64; 1276,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>101,3; 1069,28</t>
+          <t>105,91; 885,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>161,63; 1299,09</t>
+          <t>106,96; 398,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>5,15</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,44</t>
+          <t>5,27; 10,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,49</t>
+          <t>2,37; 6,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,34</t>
+          <t>2,08; 5,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,73</t>
+          <t>3,11; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>148,57; 440,53</t>
+          <t>139,8; 425,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,83; 452,35</t>
+          <t>76,33; 446,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>101,08; 633,54</t>
+          <t>124,25; 704,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,37; 123,71</t>
+          <t>45,43; 164,42</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,01</t>
+          <t>12,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>415,78%</t>
+          <t>537,12%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,71</t>
+          <t>1,23; 7,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,83</t>
+          <t>7,23; 12,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,43</t>
+          <t>3,95; 8,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,05; 13,76</t>
+          <t>10,33; 14,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,47; 242,02</t>
+          <t>13,36; 236,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>395,35; 4563,02</t>
+          <t>396,27; 4811,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>134,32; 737,37</t>
+          <t>131,5; 706,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>189,51; 817,36</t>
+          <t>291,98; 971,41</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4105,77%</t>
+          <t>3660,14%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,42; 14,79</t>
+          <t>10,43; 14,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,47; 13,32</t>
+          <t>9,44; 13,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 8,64</t>
+          <t>4,98; 8,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 11,29</t>
+          <t>7,21; 10,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>495,1; —</t>
+          <t>483,71; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,42</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>178,76%</t>
+          <t>179,55%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 9,04</t>
+          <t>6,63; 9,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,26</t>
+          <t>6,25; 8,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,58</t>
+          <t>3,59; 5,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,84</t>
+          <t>5,93; 8,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>183,43; 350,03</t>
+          <t>185,47; 351,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>408,2; 951,87</t>
+          <t>406,14; 925,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>187,74; 460,38</t>
+          <t>192,4; 443,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>119,69; 269,39</t>
+          <t>135,99; 232,47</t>
         </is>
       </c>
     </row>
